--- a/docs/03_test/部署更新画面テスト.xlsx
+++ b/docs/03_test/部署更新画面テスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7298B9-F258-4D2E-BF27-4559C4DC1EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC648C0-2C88-4F8F-866A-DFAC387373C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
@@ -130,16 +130,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部署登録画面の入力フォーム</t>
-    <rPh sb="0" eb="6">
-      <t>ブショトウロクガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テストケース</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -448,6 +438,22 @@
   </si>
   <si>
     <t>No.11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署更新画面の入力フォーム</t>
+    <rPh sb="0" eb="2">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -601,16 +607,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1612,13 +1618,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="3"/>
@@ -1626,10 +1632,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -1637,33 +1643,33 @@
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>17</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>18</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -1684,30 +1690,30 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="13"/>
+      <c r="A32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="11"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10" t="s">
+      <c r="B33" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="10"/>
+      <c r="E33" s="12"/>
       <c r="F33" s="8" t="s">
         <v>4</v>
       </c>
@@ -1740,19 +1746,19 @@
         <v>101</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1763,19 +1769,19 @@
         <v>101</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36" s="4">
         <v>99</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1786,19 +1792,19 @@
         <v>101</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" s="4">
         <v>1000</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1809,19 +1815,19 @@
         <v>101</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1832,7 +1838,7 @@
         <v>101</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" s="4">
         <v>110</v>
@@ -1841,10 +1847,10 @@
         <v>3</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1855,19 +1861,19 @@
         <v>101</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D40" s="4">
         <v>110</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1878,19 +1884,19 @@
         <v>101</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" s="4">
         <v>110</v>
       </c>
       <c r="E41" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G41" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1901,7 +1907,7 @@
         <v>101</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" s="4">
         <v>102</v>
@@ -1910,10 +1916,10 @@
         <v>6</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1930,13 +1936,13 @@
         <v>101</v>
       </c>
       <c r="E43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1953,13 +1959,13 @@
         <v>110</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1976,75 +1982,75 @@
         <v>101</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/部署更新画面テスト.xlsx
+++ b/docs/03_test/部署更新画面テスト.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC648C0-2C88-4F8F-866A-DFAC387373C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF6FE34-DB1E-4514-A2D0-C6CCAADF7CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
   <sheets>
-    <sheet name="部署登録テスト" sheetId="1" r:id="rId1"/>
+    <sheet name="部署更新テスト" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
